--- a/reports/Rolling-Plan-NoStock-2026-10-26.xlsx
+++ b/reports/Rolling-Plan-NoStock-2026-10-26.xlsx
@@ -555,7 +555,7 @@
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>Plant (coil sits here)</t>
+          <t>Plant (coil sits here) + MT</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>Coil available: yard MT</t>
+          <t>Coil of this spec in the region, yard MT (gross)</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>Coil available: mother MT</t>
+          <t>…mother MT (gross)</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Hyderabad 18.9</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Hyderabad + Lepakshi</t>
+          <t>Lepakshi 27.2 + Hyderabad 4.0</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
@@ -812,12 +812,12 @@
       </c>
       <c r="Q8" s="6" t="inlineStr">
         <is>
-          <t>30 / 8 MT ✓</t>
+          <t>30 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S8" s="6" t="inlineStr">
@@ -855,7 +855,7 @@
       </c>
       <c r="D9" s="8" t="inlineStr">
         <is>
-          <t>Lepakshi + Hyderabad</t>
+          <t>Hyderabad 8.8 + Lepakshi 3.7</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -904,12 +904,12 @@
       </c>
       <c r="Q9" s="8" t="inlineStr">
         <is>
-          <t>12 / 8 MT ✓</t>
+          <t>12 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R9" s="8" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Lepakshi + Hyderabad</t>
+          <t>Lepakshi 7.1 + Hyderabad 1.2</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="D11" s="8" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Hyderabad 14.6</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Hyderabad 14.6</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1159,7 +1159,7 @@
         <v>14.6</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>14.6</v>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="D13" s="8" t="inlineStr">
         <is>
-          <t>Lepakshi + Hyderabad</t>
+          <t>Hyderabad 27.1 + Lepakshi 15.6</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Hyderabad 12.5</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1344,10 +1344,10 @@
         </is>
       </c>
       <c r="J14" s="7" t="n">
-        <v>0</v>
+        <v>27.72</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>166.94</v>
+        <v>196.51</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>0</v>
@@ -1411,7 +1411,7 @@
       </c>
       <c r="D15" s="8" t="inlineStr">
         <is>
-          <t>Lepakshi + Hyderabad</t>
+          <t>Hyderabad 14.3 + Lepakshi 8.6</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Hyderabad</t>
+          <t>Hyderabad 8.3</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>4.12</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>125.61</v>
+        <v>149.12</v>
       </c>
       <c r="L16" s="7" t="n">
         <v>4.12</v>
@@ -1595,7 +1595,7 @@
       </c>
       <c r="D17" s="8" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 15.6</t>
         </is>
       </c>
       <c r="E17" s="8" t="inlineStr">
@@ -1687,7 +1687,7 @@
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 11.5</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -1715,7 +1715,7 @@
         <v>1.73</v>
       </c>
       <c r="K18" s="7" t="n">
-        <v>391.12</v>
+        <v>406.75</v>
       </c>
       <c r="L18" s="7" t="n">
         <v>1.73</v>
@@ -1779,7 +1779,7 @@
       </c>
       <c r="D19" s="8" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 14.6</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="Q19" s="8" t="inlineStr">
         <is>
-          <t>14 / 8 MT ✓</t>
+          <t>14 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R19" s="8" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S19" s="8" t="inlineStr">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Tapi + NPMD</t>
+          <t>NPMD 10.5 + Tapi 2.0</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -1963,7 +1963,7 @@
       </c>
       <c r="D21" s="8" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 39.6</t>
         </is>
       </c>
       <c r="E21" s="8" t="inlineStr">
@@ -1991,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="K21" s="9" t="n">
-        <v>381.39</v>
+        <v>406.75</v>
       </c>
       <c r="L21" s="9" t="n">
         <v>0</v>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 22.9</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2083,7 +2083,7 @@
         <v>0</v>
       </c>
       <c r="K22" s="7" t="n">
-        <v>34.42</v>
+        <v>49</v>
       </c>
       <c r="L22" s="7" t="n">
         <v>0</v>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 55.2</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -2175,7 +2175,7 @@
         <v>26.73</v>
       </c>
       <c r="K23" s="9" t="n">
-        <v>65.45999999999999</v>
+        <v>75.97</v>
       </c>
       <c r="L23" s="9" t="n">
         <v>26.73</v>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 18.8</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -2267,7 +2267,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="7" t="n">
-        <v>36.98</v>
+        <v>75.97</v>
       </c>
       <c r="L24" s="7" t="n">
         <v>0</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="D25" s="8" t="inlineStr">
         <is>
-          <t>Tapi</t>
+          <t>Tapi 14.6</t>
         </is>
       </c>
       <c r="E25" s="8" t="inlineStr">
@@ -2423,7 +2423,7 @@
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Tapi</t>
+          <t>Tapi 13.5</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 21.9</t>
         </is>
       </c>
       <c r="E27" s="8" t="inlineStr">
@@ -2543,7 +2543,7 @@
         <v>4.68</v>
       </c>
       <c r="K27" s="9" t="n">
-        <v>341.8</v>
+        <v>406.75</v>
       </c>
       <c r="L27" s="9" t="n">
         <v>4.68</v>
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Tapi</t>
+          <t>Tapi 16.7</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -2699,7 +2699,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Tapi</t>
+          <t>Tapi 11.4</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 34.4</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="K30" s="7" t="n">
-        <v>324.61</v>
+        <v>406.75</v>
       </c>
       <c r="L30" s="7" t="n">
         <v>0</v>
@@ -2887,7 +2887,7 @@
       </c>
       <c r="D31" s="8" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 10.4</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -2915,7 +2915,7 @@
         <v>0</v>
       </c>
       <c r="K31" s="9" t="n">
-        <v>290.24</v>
+        <v>406.75</v>
       </c>
       <c r="L31" s="9" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>NPMD</t>
+          <t>NPMD 11.5</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -3007,7 +3007,7 @@
         <v>0</v>
       </c>
       <c r="K32" s="7" t="n">
-        <v>11.5</v>
+        <v>49</v>
       </c>
       <c r="L32" s="7" t="n">
         <v>0</v>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Tapi</t>
+          <t>Tapi 18.9</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="11" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L35" s="11" t="n">
         <v>0</v>
@@ -3357,18 +3357,18 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>50x25</t>
+          <t>40x20</t>
         </is>
       </c>
       <c r="G36" s="10" t="n">
         <v>1.2</v>
       </c>
       <c r="H36" s="11" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="I36" s="10" t="inlineStr">
         <is>
-          <t>1.2 × 148 mm</t>
+          <t>1.2 × 117 mm</t>
         </is>
       </c>
       <c r="J36" s="11" t="n">
@@ -3387,26 +3387,26 @@
         <v>0</v>
       </c>
       <c r="O36" s="11" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="P36" s="10" t="inlineStr">
         <is>
-          <t>37 / 20 MT ✓</t>
+          <t>46 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q36" s="10" t="inlineStr">
         <is>
-          <t>23 / 12 MT ✓</t>
+          <t>10 / 8 MT ✓</t>
         </is>
       </c>
       <c r="R36" s="10" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>NO COIL — order 1.2 mm × 148 mm</t>
+          <t>NO COIL — order 1.2 mm × 117 mm</t>
         </is>
       </c>
       <c r="T36" s="10" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="V36" s="10" t="inlineStr">
         <is>
-          <t>South width from its own 1.6mm run (1.2mm never run here)</t>
+          <t>South has slit this 18 of 18 times</t>
         </is>
       </c>
     </row>
@@ -3453,14 +3453,14 @@
         </is>
       </c>
       <c r="G37" s="10" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="H37" s="11" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="I37" s="10" t="inlineStr">
         <is>
-          <t>1.6 × 148 mm</t>
+          <t>1.2 × 148 mm</t>
         </is>
       </c>
       <c r="J37" s="11" t="n">
@@ -3479,7 +3479,7 @@
         <v>0</v>
       </c>
       <c r="O37" s="11" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="P37" s="10" t="inlineStr">
         <is>
@@ -3488,17 +3488,17 @@
       </c>
       <c r="Q37" s="10" t="inlineStr">
         <is>
-          <t>14 / 8 MT ✓</t>
+          <t>23 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R37" s="10" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>NO COIL — order 1.6 mm × 148 mm</t>
+          <t>NO COIL — order 1.2 mm × 148 mm</t>
         </is>
       </c>
       <c r="T37" s="10" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="V37" s="10" t="inlineStr">
         <is>
-          <t>South has slit this 27 of 38 times</t>
+          <t>South width from its own 1.6mm run (1.2mm never run here)</t>
         </is>
       </c>
     </row>
@@ -3541,25 +3541,25 @@
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>60x40</t>
+          <t>50x25</t>
         </is>
       </c>
       <c r="G38" s="10" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="H38" s="11" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="I38" s="10" t="inlineStr">
         <is>
-          <t>1.2 × 197 mm</t>
+          <t>1.6 × 148 mm</t>
         </is>
       </c>
       <c r="J38" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L38" s="11" t="n">
         <v>0</v>
@@ -3571,26 +3571,26 @@
         <v>0</v>
       </c>
       <c r="O38" s="11" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="P38" s="10" t="inlineStr">
         <is>
-          <t>68 / 20 MT ✓</t>
+          <t>37 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q38" s="10" t="inlineStr">
         <is>
-          <t>32 / 12 MT ✓</t>
+          <t>14 / 8 MT ✓</t>
         </is>
       </c>
       <c r="R38" s="10" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>NO COIL — order 1.2 mm × 197 mm</t>
+          <t>NO COIL — order 1.6 mm × 148 mm</t>
         </is>
       </c>
       <c r="T38" s="10" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="V38" s="10" t="inlineStr">
         <is>
-          <t>South width from its own 1.6mm run (1.2mm never run here)</t>
+          <t>South has slit this 27 of 38 times</t>
         </is>
       </c>
     </row>
@@ -3633,14 +3633,14 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>75x25</t>
+          <t>60x40</t>
         </is>
       </c>
       <c r="G39" s="10" t="n">
         <v>1.2</v>
       </c>
       <c r="H39" s="11" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="I39" s="10" t="inlineStr">
         <is>
@@ -3663,16 +3663,16 @@
         <v>0</v>
       </c>
       <c r="O39" s="11" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="P39" s="10" t="inlineStr">
         <is>
-          <t>34 / 20 MT ✓</t>
+          <t>68 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q39" s="10" t="inlineStr">
         <is>
-          <t>20 / 12 MT ✓</t>
+          <t>32 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R39" s="10" t="inlineStr">
@@ -3725,18 +3725,18 @@
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>60x40</t>
+          <t>75x25</t>
         </is>
       </c>
       <c r="G40" s="10" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="H40" s="11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="I40" s="10" t="inlineStr">
         <is>
-          <t>1.6 × 197 mm</t>
+          <t>1.2 × 197 mm</t>
         </is>
       </c>
       <c r="J40" s="11" t="n">
@@ -3755,16 +3755,16 @@
         <v>0</v>
       </c>
       <c r="O40" s="11" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="P40" s="10" t="inlineStr">
         <is>
-          <t>68 / 20 MT ✓</t>
+          <t>34 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q40" s="10" t="inlineStr">
         <is>
-          <t>28 / 12 MT ✓</t>
+          <t>20 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R40" s="10" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>NO COIL — order 1.6 mm × 197 mm</t>
+          <t>NO COIL — order 1.2 mm × 197 mm</t>
         </is>
       </c>
       <c r="T40" s="10" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="V40" s="10" t="inlineStr">
         <is>
-          <t>South has slit this 64 of 64 times</t>
+          <t>South width from its own 1.6mm run (1.2mm never run here)</t>
         </is>
       </c>
     </row>
@@ -3817,14 +3817,14 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>75x25</t>
+          <t>60x40</t>
         </is>
       </c>
       <c r="G41" s="10" t="n">
         <v>1.6</v>
       </c>
       <c r="H41" s="11" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="I41" s="10" t="inlineStr">
         <is>
@@ -3835,7 +3835,7 @@
         <v>0</v>
       </c>
       <c r="K41" s="11" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L41" s="11" t="n">
         <v>0</v>
@@ -3847,16 +3847,16 @@
         <v>0</v>
       </c>
       <c r="O41" s="11" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="P41" s="10" t="inlineStr">
         <is>
-          <t>34 / 20 MT ✓</t>
+          <t>68 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q41" s="10" t="inlineStr">
         <is>
-          <t>14 / 12 MT ✓</t>
+          <t>28 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R41" s="10" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="V41" s="10" t="inlineStr">
         <is>
-          <t>South has slit this 22 of 22 times</t>
+          <t>South has slit this 64 of 64 times</t>
         </is>
       </c>
     </row>
@@ -3909,25 +3909,25 @@
       </c>
       <c r="F42" s="10" t="inlineStr">
         <is>
-          <t>80x40</t>
+          <t>75x25</t>
         </is>
       </c>
       <c r="G42" s="10" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="H42" s="11" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="I42" s="10" t="inlineStr">
         <is>
-          <t>1.2 × 237 mm</t>
+          <t>1.6 × 197 mm</t>
         </is>
       </c>
       <c r="J42" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L42" s="11" t="n">
         <v>0</v>
@@ -3939,16 +3939,16 @@
         <v>0</v>
       </c>
       <c r="O42" s="11" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="P42" s="10" t="inlineStr">
         <is>
-          <t>97 / 20 MT ✓</t>
+          <t>34 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q42" s="10" t="inlineStr">
         <is>
-          <t>19 / 12 MT ✓</t>
+          <t>14 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R42" s="10" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>NO COIL — order 1.2 mm × 237 mm</t>
+          <t>NO COIL — order 1.6 mm × 197 mm</t>
         </is>
       </c>
       <c r="T42" s="10" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="V42" s="10" t="inlineStr">
         <is>
-          <t>South width from its own 1.6mm run (1.2mm never run here)</t>
+          <t>South has slit this 22 of 22 times</t>
         </is>
       </c>
     </row>
@@ -4001,18 +4001,18 @@
       </c>
       <c r="F43" s="10" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>80x40</t>
         </is>
       </c>
       <c r="G43" s="10" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="H43" s="11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="I43" s="10" t="inlineStr">
         <is>
-          <t>1.6 × 286 mm</t>
+          <t>1.2 × 237 mm</t>
         </is>
       </c>
       <c r="J43" s="11" t="n">
@@ -4031,16 +4031,16 @@
         <v>0</v>
       </c>
       <c r="O43" s="11" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="P43" s="10" t="inlineStr">
         <is>
-          <t>43 / 20 MT ✓</t>
+          <t>97 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q43" s="10" t="inlineStr">
         <is>
-          <t>37 / 12 MT ✓</t>
+          <t>19 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R43" s="10" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>NO COIL — order 1.6 mm × 286 mm</t>
+          <t>NO COIL — order 1.2 mm × 237 mm</t>
         </is>
       </c>
       <c r="T43" s="10" t="inlineStr">
@@ -4065,7 +4065,7 @@
       </c>
       <c r="V43" s="10" t="inlineStr">
         <is>
-          <t>South width from its own 2mm run (1.6mm never run here)</t>
+          <t>South width from its own 1.6mm run (1.2mm never run here)</t>
         </is>
       </c>
     </row>
@@ -4093,25 +4093,25 @@
       </c>
       <c r="F44" s="10" t="inlineStr">
         <is>
-          <t>100x50</t>
+          <t>96x48</t>
         </is>
       </c>
       <c r="G44" s="10" t="n">
         <v>1.6</v>
       </c>
       <c r="H44" s="11" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="I44" s="10" t="inlineStr">
         <is>
-          <t>1.6 × 296 mm</t>
+          <t>1.6 × 286 mm</t>
         </is>
       </c>
       <c r="J44" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L44" s="11" t="n">
         <v>0</v>
@@ -4123,16 +4123,16 @@
         <v>0</v>
       </c>
       <c r="O44" s="11" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="P44" s="10" t="inlineStr">
         <is>
-          <t>51 / 20 MT ✓</t>
+          <t>43 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q44" s="10" t="inlineStr">
         <is>
-          <t>46 / 12 MT ✓</t>
+          <t>37 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R44" s="10" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>NO COIL — order 1.6 mm × 296 mm</t>
+          <t>NO COIL — order 1.6 mm × 286 mm</t>
         </is>
       </c>
       <c r="T44" s="10" t="inlineStr">
@@ -4157,7 +4157,7 @@
       </c>
       <c r="V44" s="10" t="inlineStr">
         <is>
-          <t>South has slit this 9 of 18 times</t>
+          <t>South width from its own 2mm run (1.6mm never run here)</t>
         </is>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
       <c r="B45" s="10" t="inlineStr"/>
       <c r="C45" s="10" t="inlineStr">
         <is>
-          <t>WEST</t>
+          <t>SOUTH</t>
         </is>
       </c>
       <c r="D45" s="10" t="inlineStr">
@@ -4180,30 +4180,30 @@
       </c>
       <c r="E45" s="10" t="inlineStr">
         <is>
-          <t>SHS</t>
+          <t>RHS</t>
         </is>
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>20x20</t>
+          <t>100x50</t>
         </is>
       </c>
       <c r="G45" s="10" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H45" s="11" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="I45" s="10" t="inlineStr">
         <is>
-          <t>2 × 76 mm</t>
+          <t>1.6 × 296 mm</t>
         </is>
       </c>
       <c r="J45" s="11" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="11" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L45" s="11" t="n">
         <v>0</v>
@@ -4215,26 +4215,26 @@
         <v>0</v>
       </c>
       <c r="O45" s="11" t="n">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="P45" s="10" t="inlineStr">
         <is>
-          <t>27 / 20 MT ✓</t>
+          <t>51 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q45" s="10" t="inlineStr">
         <is>
-          <t>9 / 8 MT ✓</t>
+          <t>46 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R45" s="10" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>NO COIL — order 2 mm × 76 mm</t>
+          <t>NO COIL — order 1.6 mm × 296 mm</t>
         </is>
       </c>
       <c r="T45" s="10" t="inlineStr">
@@ -4249,7 +4249,7 @@
       </c>
       <c r="V45" s="10" t="inlineStr">
         <is>
-          <t>company-wide width — West has never run this size</t>
+          <t>South has slit this 9 of 18 times</t>
         </is>
       </c>
     </row>
@@ -4592,12 +4592,12 @@
       </c>
       <c r="Q49" s="10" t="inlineStr">
         <is>
-          <t>42 / 8 MT ✓</t>
+          <t>42 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R49" s="10" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S49" s="10" t="inlineStr">
@@ -6995,7 +6995,7 @@
         <v>0</v>
       </c>
       <c r="K76" s="11" t="n">
-        <v>0.21</v>
+        <v>27.43</v>
       </c>
       <c r="L76" s="11" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>181.93</v>
+        <v>196.51</v>
       </c>
       <c r="L77" s="11" t="n">
         <v>0</v>
@@ -7171,7 +7171,7 @@
         <v>0</v>
       </c>
       <c r="K78" s="11" t="n">
-        <v>0.21</v>
+        <v>27.43</v>
       </c>
       <c r="L78" s="11" t="n">
         <v>0</v>
@@ -7699,7 +7699,7 @@
         <v>0</v>
       </c>
       <c r="K84" s="11" t="n">
-        <v>381.39</v>
+        <v>406.75</v>
       </c>
       <c r="L84" s="11" t="n">
         <v>0</v>
@@ -7875,7 +7875,7 @@
         <v>0</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>34.42</v>
+        <v>49</v>
       </c>
       <c r="L86" s="11" t="n">
         <v>0</v>
@@ -7963,7 +7963,7 @@
         <v>0</v>
       </c>
       <c r="K87" s="11" t="n">
-        <v>65.45999999999999</v>
+        <v>75.97</v>
       </c>
       <c r="L87" s="11" t="n">
         <v>0</v>
@@ -7984,12 +7984,12 @@
       </c>
       <c r="Q87" s="10" t="inlineStr">
         <is>
-          <t>11 / 8 MT ✓</t>
+          <t>11 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R87" s="10" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S87" s="10" t="inlineStr">
@@ -8315,7 +8315,7 @@
         <v>0</v>
       </c>
       <c r="K91" s="11" t="n">
-        <v>18.23</v>
+        <v>75.97</v>
       </c>
       <c r="L91" s="11" t="n">
         <v>0</v>
@@ -9216,12 +9216,12 @@
       </c>
       <c r="Q101" s="10" t="inlineStr">
         <is>
-          <t>2 / 8 MT ✗</t>
+          <t>2 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R101" s="10" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S101" s="10" t="inlineStr">
@@ -9547,7 +9547,7 @@
         <v>0</v>
       </c>
       <c r="K105" s="11" t="n">
-        <v>18.23</v>
+        <v>75.97</v>
       </c>
       <c r="L105" s="11" t="n">
         <v>0</v>
@@ -9744,12 +9744,12 @@
       </c>
       <c r="Q107" s="10" t="inlineStr">
         <is>
-          <t>10 / 12 MT ✗</t>
+          <t>10 / 8 MT ✓</t>
         </is>
       </c>
       <c r="R107" s="10" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S107" s="10" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="Q117" s="4" t="inlineStr">
         <is>
-          <t>5 / 8 MT ✗</t>
+          <t>5 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R117" s="4" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S117" s="4" t="inlineStr">
@@ -10875,7 +10875,7 @@
         <v>1.57</v>
       </c>
       <c r="K120" s="5" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L120" s="5" t="n">
         <v>0</v>
@@ -10988,12 +10988,12 @@
       </c>
       <c r="Q121" s="4" t="inlineStr">
         <is>
-          <t>5 / 12 MT ✗</t>
+          <t>5 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R121" s="4" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S121" s="4" t="inlineStr">
@@ -11055,7 +11055,7 @@
         <v>4.22</v>
       </c>
       <c r="K122" s="5" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L122" s="5" t="n">
         <v>0</v>
@@ -11147,7 +11147,7 @@
         <v>3.89</v>
       </c>
       <c r="K123" s="5" t="n">
-        <v>0.21</v>
+        <v>27.43</v>
       </c>
       <c r="L123" s="5" t="n">
         <v>0</v>
@@ -11348,12 +11348,12 @@
       </c>
       <c r="Q125" s="4" t="inlineStr">
         <is>
-          <t>4 / 8 MT ✗</t>
+          <t>4 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R125" s="4" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S125" s="4" t="inlineStr">
@@ -11436,12 +11436,12 @@
       </c>
       <c r="Q126" s="4" t="inlineStr">
         <is>
-          <t>10 / 8 MT ✓</t>
+          <t>10 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R126" s="4" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S126" s="4" t="inlineStr">
@@ -11503,7 +11503,7 @@
         <v>12.33</v>
       </c>
       <c r="K127" s="5" t="n">
-        <v>0.21</v>
+        <v>27.43</v>
       </c>
       <c r="L127" s="5" t="n">
         <v>0</v>
@@ -11855,7 +11855,7 @@
         <v>0</v>
       </c>
       <c r="K131" s="5" t="n">
-        <v>0.21</v>
+        <v>27.43</v>
       </c>
       <c r="L131" s="5" t="n">
         <v>0</v>
@@ -12056,12 +12056,12 @@
       </c>
       <c r="Q133" s="4" t="inlineStr">
         <is>
-          <t>5 / 12 MT ✗</t>
+          <t>5 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R133" s="4" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S133" s="4" t="inlineStr">
@@ -12123,7 +12123,7 @@
         <v>0</v>
       </c>
       <c r="K134" s="5" t="n">
-        <v>0.21</v>
+        <v>27.43</v>
       </c>
       <c r="L134" s="5" t="n">
         <v>0</v>
@@ -12211,7 +12211,7 @@
         <v>0</v>
       </c>
       <c r="K135" s="5" t="n">
-        <v>71.91</v>
+        <v>90.47</v>
       </c>
       <c r="L135" s="5" t="n">
         <v>0</v>
@@ -12373,21 +12373,21 @@
         </is>
       </c>
       <c r="G137" s="4" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="H137" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I137" s="4" t="inlineStr">
         <is>
-          <t>1.2 × 117 mm</t>
+          <t>1.6 × 116 mm</t>
         </is>
       </c>
       <c r="J137" s="5" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="K137" s="5" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L137" s="5" t="n">
         <v>0</v>
@@ -12399,7 +12399,7 @@
         <v>0</v>
       </c>
       <c r="O137" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
@@ -12408,17 +12408,17 @@
       </c>
       <c r="Q137" s="4" t="inlineStr">
         <is>
-          <t>10 / 12 MT ✗</t>
+          <t>30 / 8 MT ✓</t>
         </is>
       </c>
       <c r="R137" s="4" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S137" s="4" t="inlineStr">
         <is>
-          <t>DEFER — under gauge floor</t>
+          <t>DEFER — only 4.1 MT of coil, under the 8 MT gauge floor</t>
         </is>
       </c>
       <c r="T137" s="4" t="inlineStr">
@@ -12426,10 +12426,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="U137" s="4" t="inlineStr"/>
+      <c r="U137" s="4" t="inlineStr">
+        <is>
+          <t>07 Nov 2026</t>
+        </is>
+      </c>
       <c r="V137" s="4" t="inlineStr">
         <is>
-          <t>South has slit this 18 of 18 times</t>
+          <t>South has slit this 12 of 27 times</t>
         </is>
       </c>
     </row>
@@ -12461,21 +12465,21 @@
         </is>
       </c>
       <c r="G138" s="4" t="n">
-        <v>1.6</v>
+        <v>2.5</v>
       </c>
       <c r="H138" s="5" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="I138" s="4" t="inlineStr">
         <is>
-          <t>1.6 × 116 mm</t>
+          <t>2.5 × 114 mm</t>
         </is>
       </c>
       <c r="J138" s="5" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="K138" s="5" t="n">
-        <v>0</v>
+        <v>90.47</v>
       </c>
       <c r="L138" s="5" t="n">
         <v>0</v>
@@ -12487,7 +12491,7 @@
         <v>0</v>
       </c>
       <c r="O138" s="5" t="n">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
@@ -12496,7 +12500,7 @@
       </c>
       <c r="Q138" s="4" t="inlineStr">
         <is>
-          <t>30 / 8 MT ✓</t>
+          <t>6 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R138" s="4" t="inlineStr">
@@ -12506,7 +12510,7 @@
       </c>
       <c r="S138" s="4" t="inlineStr">
         <is>
-          <t>DEFER — only 4.1 MT of coil, under the 8 MT gauge floor</t>
+          <t>DEFER — under gauge floor</t>
         </is>
       </c>
       <c r="T138" s="4" t="inlineStr">
@@ -12514,14 +12518,10 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="U138" s="4" t="inlineStr">
-        <is>
-          <t>07 Nov 2026</t>
-        </is>
-      </c>
+      <c r="U138" s="4" t="inlineStr"/>
       <c r="V138" s="4" t="inlineStr">
         <is>
-          <t>South has slit this 12 of 27 times</t>
+          <t>South has slit this 9 of 12 times</t>
         </is>
       </c>
     </row>
@@ -12549,25 +12549,25 @@
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>40x20</t>
+          <t>60x40</t>
         </is>
       </c>
       <c r="G139" s="4" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="H139" s="5" t="n">
         <v>6</v>
       </c>
       <c r="I139" s="4" t="inlineStr">
         <is>
-          <t>2.5 × 114 mm</t>
+          <t>3 × 196 mm</t>
         </is>
       </c>
       <c r="J139" s="5" t="n">
-        <v>0</v>
+        <v>13.16</v>
       </c>
       <c r="K139" s="5" t="n">
-        <v>71.91</v>
+        <v>149.12</v>
       </c>
       <c r="L139" s="5" t="n">
         <v>0</v>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>46 / 20 MT ✓</t>
+          <t>68 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q139" s="4" t="inlineStr">
@@ -12609,7 +12609,7 @@
       <c r="U139" s="4" t="inlineStr"/>
       <c r="V139" s="4" t="inlineStr">
         <is>
-          <t>South has slit this 9 of 12 times</t>
+          <t>South width from its own 2.8mm run (3mm never run here)</t>
         </is>
       </c>
     </row>
@@ -12641,21 +12641,21 @@
         </is>
       </c>
       <c r="G140" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H140" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I140" s="4" t="inlineStr">
         <is>
-          <t>3 × 196 mm</t>
+          <t>4 × 196 mm</t>
         </is>
       </c>
       <c r="J140" s="5" t="n">
-        <v>4.83</v>
+        <v>0</v>
       </c>
       <c r="K140" s="5" t="n">
-        <v>125.61</v>
+        <v>0</v>
       </c>
       <c r="L140" s="5" t="n">
         <v>0</v>
@@ -12667,7 +12667,7 @@
         <v>0</v>
       </c>
       <c r="O140" s="5" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
@@ -12676,7 +12676,7 @@
       </c>
       <c r="Q140" s="4" t="inlineStr">
         <is>
-          <t>6 / 8 MT ✗</t>
+          <t>2 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R140" s="4" t="inlineStr">
@@ -12697,7 +12697,7 @@
       <c r="U140" s="4" t="inlineStr"/>
       <c r="V140" s="4" t="inlineStr">
         <is>
-          <t>South width from its own 2.8mm run (3mm never run here)</t>
+          <t>South width from its own 2.8mm run (4mm never run here)</t>
         </is>
       </c>
     </row>
@@ -12725,25 +12725,25 @@
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>60x40</t>
+          <t>80x40</t>
         </is>
       </c>
       <c r="G141" s="4" t="n">
-        <v>4</v>
+        <v>1.6</v>
       </c>
       <c r="H141" s="5" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="I141" s="4" t="inlineStr">
         <is>
-          <t>4 × 196 mm</t>
+          <t>1.6 × 237 mm</t>
         </is>
       </c>
       <c r="J141" s="5" t="n">
-        <v>0</v>
+        <v>7.66</v>
       </c>
       <c r="K141" s="5" t="n">
-        <v>0</v>
+        <v>18.88</v>
       </c>
       <c r="L141" s="5" t="n">
         <v>0</v>
@@ -12755,26 +12755,26 @@
         <v>0</v>
       </c>
       <c r="O141" s="5" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>68 / 20 MT ✓</t>
+          <t>97 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q141" s="4" t="inlineStr">
         <is>
-          <t>2 / 8 MT ✗</t>
+          <t>70 / 12 MT ✓</t>
         </is>
       </c>
       <c r="R141" s="4" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S141" s="4" t="inlineStr">
         <is>
-          <t>DEFER — under gauge floor</t>
+          <t>DEFER — only 7.4 MT of coil, under the 12 MT gauge floor</t>
         </is>
       </c>
       <c r="T141" s="4" t="inlineStr">
@@ -12782,10 +12782,14 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="U141" s="4" t="inlineStr"/>
+      <c r="U141" s="4" t="inlineStr">
+        <is>
+          <t>07 Nov 2026</t>
+        </is>
+      </c>
       <c r="V141" s="4" t="inlineStr">
         <is>
-          <t>South width from its own 2.8mm run (4mm never run here)</t>
+          <t>South has slit this 20 of 32 times</t>
         </is>
       </c>
     </row>
@@ -12813,25 +12817,25 @@
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>80x40</t>
+          <t>96x48</t>
         </is>
       </c>
       <c r="G142" s="4" t="n">
-        <v>1.6</v>
+        <v>2.8</v>
       </c>
       <c r="H142" s="5" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="I142" s="4" t="inlineStr">
         <is>
-          <t>1.6 × 237 mm</t>
+          <t>2.8 × 280 mm</t>
         </is>
       </c>
       <c r="J142" s="5" t="n">
-        <v>7.66</v>
+        <v>0</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>0</v>
+        <v>196.51</v>
       </c>
       <c r="L142" s="5" t="n">
         <v>0</v>
@@ -12843,26 +12847,26 @@
         <v>0</v>
       </c>
       <c r="O142" s="5" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>97 / 20 MT ✓</t>
+          <t>43 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q142" s="4" t="inlineStr">
         <is>
-          <t>70 / 12 MT ✓</t>
+          <t>6 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R142" s="4" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S142" s="4" t="inlineStr">
         <is>
-          <t>DEFER — only 7.4 MT of coil, under the 12 MT gauge floor</t>
+          <t>DEFER — under gauge floor</t>
         </is>
       </c>
       <c r="T142" s="4" t="inlineStr">
@@ -12870,14 +12874,10 @@
           <t>ok</t>
         </is>
       </c>
-      <c r="U142" s="4" t="inlineStr">
-        <is>
-          <t>07 Nov 2026</t>
-        </is>
-      </c>
+      <c r="U142" s="4" t="inlineStr"/>
       <c r="V142" s="4" t="inlineStr">
         <is>
-          <t>South has slit this 20 of 32 times</t>
+          <t>South width from its own 3mm run (2.8mm never run here)</t>
         </is>
       </c>
     </row>
@@ -12905,25 +12905,25 @@
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>96x48</t>
+          <t>100x50</t>
         </is>
       </c>
       <c r="G143" s="4" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="H143" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I143" s="4" t="inlineStr">
         <is>
-          <t>2.8 × 280 mm</t>
+          <t>2.9 × 295 mm</t>
         </is>
       </c>
       <c r="J143" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>154.44</v>
+        <v>149.12</v>
       </c>
       <c r="L143" s="5" t="n">
         <v>0</v>
@@ -12935,21 +12935,21 @@
         <v>0</v>
       </c>
       <c r="O143" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>43 / 20 MT ✓</t>
+          <t>51 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q143" s="4" t="inlineStr">
         <is>
-          <t>6 / 12 MT ✗</t>
+          <t>5 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R143" s="4" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S143" s="4" t="inlineStr">
@@ -12965,7 +12965,7 @@
       <c r="U143" s="4" t="inlineStr"/>
       <c r="V143" s="4" t="inlineStr">
         <is>
-          <t>South width from its own 3mm run (2.8mm never run here)</t>
+          <t>South width from its own 2.8mm run (2.9mm never run here)</t>
         </is>
       </c>
     </row>
@@ -12993,25 +12993,25 @@
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>100x50</t>
+          <t>145x82</t>
         </is>
       </c>
       <c r="G144" s="4" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H144" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I144" s="4" t="inlineStr">
         <is>
-          <t>2.9 × 295 mm</t>
+          <t>3 × 448 mm</t>
         </is>
       </c>
       <c r="J144" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K144" s="5" t="n">
-        <v>121.4</v>
+        <v>149.12</v>
       </c>
       <c r="L144" s="5" t="n">
         <v>0</v>
@@ -13023,16 +13023,16 @@
         <v>0</v>
       </c>
       <c r="O144" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>51 / 20 MT ✓</t>
+          <t>11 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q144" s="4" t="inlineStr">
         <is>
-          <t>5 / 12 MT ✗</t>
+          <t>3 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R144" s="4" t="inlineStr">
@@ -13042,7 +13042,7 @@
       </c>
       <c r="S144" s="4" t="inlineStr">
         <is>
-          <t>DEFER — under gauge floor</t>
+          <t>DEFER — family short of min campaign</t>
         </is>
       </c>
       <c r="T144" s="4" t="inlineStr">
@@ -13053,7 +13053,7 @@
       <c r="U144" s="4" t="inlineStr"/>
       <c r="V144" s="4" t="inlineStr">
         <is>
-          <t>South width from its own 2.8mm run (2.9mm never run here)</t>
+          <t>company-wide width — South has never run this size</t>
         </is>
       </c>
     </row>
@@ -13085,21 +13085,21 @@
         </is>
       </c>
       <c r="G145" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H145" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I145" s="4" t="inlineStr">
         <is>
-          <t>3 × 448 mm</t>
+          <t>4 × 448 mm</t>
         </is>
       </c>
       <c r="J145" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K145" s="5" t="n">
-        <v>121.4</v>
+        <v>0</v>
       </c>
       <c r="L145" s="5" t="n">
         <v>0</v>
@@ -13111,7 +13111,7 @@
         <v>0</v>
       </c>
       <c r="O145" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
       </c>
       <c r="Q145" s="4" t="inlineStr">
         <is>
-          <t>3 / 12 MT ✗</t>
+          <t>2 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R145" s="4" t="inlineStr">
@@ -13173,21 +13173,21 @@
         </is>
       </c>
       <c r="G146" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H146" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I146" s="4" t="inlineStr">
         <is>
-          <t>4 × 448 mm</t>
+          <t>5 × 448 mm</t>
         </is>
       </c>
       <c r="J146" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K146" s="5" t="n">
-        <v>0</v>
+        <v>83.06</v>
       </c>
       <c r="L146" s="5" t="n">
         <v>0</v>
@@ -13199,7 +13199,7 @@
         <v>0</v>
       </c>
       <c r="O146" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
@@ -13208,12 +13208,12 @@
       </c>
       <c r="Q146" s="4" t="inlineStr">
         <is>
-          <t>2 / 12 MT ✗</t>
+          <t>6 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R146" s="4" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S146" s="4" t="inlineStr">
@@ -13229,7 +13229,7 @@
       <c r="U146" s="4" t="inlineStr"/>
       <c r="V146" s="4" t="inlineStr">
         <is>
-          <t>company-wide width — South has never run this size</t>
+          <t>company-wide width from 4mm — South has never run this size</t>
         </is>
       </c>
     </row>
@@ -13257,25 +13257,25 @@
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>145x82</t>
+          <t>200x100</t>
         </is>
       </c>
       <c r="G147" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="H147" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="H147" s="5" t="n">
-        <v>6</v>
-      </c>
       <c r="I147" s="4" t="inlineStr">
         <is>
-          <t>5 × 448 mm</t>
+          <t>6 × 596 mm</t>
         </is>
       </c>
       <c r="J147" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K147" s="5" t="n">
-        <v>83.06</v>
+        <v>0</v>
       </c>
       <c r="L147" s="5" t="n">
         <v>0</v>
@@ -13287,16 +13287,16 @@
         <v>0</v>
       </c>
       <c r="O147" s="5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>11 / 20 MT ✗</t>
+          <t>5 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q147" s="4" t="inlineStr">
         <is>
-          <t>6 / 8 MT ✗</t>
+          <t>5 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R147" s="4" t="inlineStr">
@@ -13317,7 +13317,7 @@
       <c r="U147" s="4" t="inlineStr"/>
       <c r="V147" s="4" t="inlineStr">
         <is>
-          <t>company-wide width from 4mm — South has never run this size</t>
+          <t>company-wide width from 5mm — South has never run this size</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13330,7 @@
       <c r="B148" s="4" t="inlineStr"/>
       <c r="C148" s="4" t="inlineStr">
         <is>
-          <t>SOUTH</t>
+          <t>WEST</t>
         </is>
       </c>
       <c r="D148" s="4" t="inlineStr">
@@ -13340,23 +13340,23 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>RHS</t>
+          <t>CHS</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
         <is>
-          <t>200x100</t>
+          <t>15 NB</t>
         </is>
       </c>
       <c r="G148" s="4" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H148" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I148" s="4" t="inlineStr">
         <is>
-          <t>6 × 596 mm</t>
+          <t>2 × 64 mm</t>
         </is>
       </c>
       <c r="J148" s="5" t="n">
@@ -13375,21 +13375,21 @@
         <v>0</v>
       </c>
       <c r="O148" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>5 / 20 MT ✗</t>
+          <t>2 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q148" s="4" t="inlineStr">
         <is>
-          <t>5 / 8 MT ✗</t>
+          <t>2 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R148" s="4" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S148" s="4" t="inlineStr">
@@ -13405,7 +13405,7 @@
       <c r="U148" s="4" t="inlineStr"/>
       <c r="V148" s="4" t="inlineStr">
         <is>
-          <t>company-wide width from 5mm — South has never run this size</t>
+          <t>company-wide width — West has never run this size</t>
         </is>
       </c>
     </row>
@@ -13433,18 +13433,18 @@
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>15 NB</t>
+          <t>20 NB</t>
         </is>
       </c>
       <c r="G149" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H149" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I149" s="4" t="inlineStr">
         <is>
-          <t>2 × 64 mm</t>
+          <t>2 × 76 mm</t>
         </is>
       </c>
       <c r="J149" s="5" t="n">
@@ -13463,21 +13463,21 @@
         <v>0</v>
       </c>
       <c r="O149" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>2 / 20 MT ✗</t>
+          <t>12 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q149" s="4" t="inlineStr">
         <is>
-          <t>2 / 12 MT ✗</t>
+          <t>7 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R149" s="4" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S149" s="4" t="inlineStr">
@@ -13521,18 +13521,18 @@
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>20 NB</t>
+          <t>25 NB</t>
         </is>
       </c>
       <c r="G150" s="4" t="n">
         <v>2</v>
       </c>
       <c r="H150" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I150" s="4" t="inlineStr">
         <is>
-          <t>2 × 76 mm</t>
+          <t>2 × 96 mm</t>
         </is>
       </c>
       <c r="J150" s="5" t="n">
@@ -13551,16 +13551,16 @@
         <v>0</v>
       </c>
       <c r="O150" s="5" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>12 / 20 MT ✗</t>
+          <t>7 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q150" s="4" t="inlineStr">
         <is>
-          <t>7 / 8 MT ✗</t>
+          <t>5 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R150" s="4" t="inlineStr">
@@ -13613,21 +13613,21 @@
         </is>
       </c>
       <c r="G151" s="4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H151" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="H151" s="5" t="n">
-        <v>5</v>
-      </c>
       <c r="I151" s="4" t="inlineStr">
         <is>
-          <t>2 × 96 mm</t>
+          <t>2.3 × 97 mm</t>
         </is>
       </c>
       <c r="J151" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K151" s="5" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L151" s="5" t="n">
         <v>0</v>
@@ -13639,7 +13639,7 @@
         <v>0</v>
       </c>
       <c r="O151" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
       </c>
       <c r="Q151" s="4" t="inlineStr">
         <is>
-          <t>5 / 8 MT ✗</t>
+          <t>2 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R151" s="4" t="inlineStr">
@@ -13697,25 +13697,25 @@
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>25 NB</t>
+          <t>32 NB</t>
         </is>
       </c>
       <c r="G152" s="4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H152" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I152" s="4" t="inlineStr">
         <is>
-          <t>2.3 × 97 mm</t>
+          <t>2 × 130 mm</t>
         </is>
       </c>
       <c r="J152" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K152" s="5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L152" s="5" t="n">
         <v>0</v>
@@ -13727,16 +13727,16 @@
         <v>0</v>
       </c>
       <c r="O152" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>7 / 20 MT ✗</t>
+          <t>11 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q152" s="4" t="inlineStr">
         <is>
-          <t>2 / 8 MT ✗</t>
+          <t>3 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R152" s="4" t="inlineStr">
@@ -13789,21 +13789,21 @@
         </is>
       </c>
       <c r="G153" s="4" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H153" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I153" s="4" t="inlineStr">
         <is>
-          <t>2 × 130 mm</t>
+          <t>2.5 × 128 mm</t>
         </is>
       </c>
       <c r="J153" s="5" t="n">
         <v>0</v>
       </c>
       <c r="K153" s="5" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L153" s="5" t="n">
         <v>0</v>
@@ -13815,7 +13815,7 @@
         <v>0</v>
       </c>
       <c r="O153" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
       </c>
       <c r="Q153" s="4" t="inlineStr">
         <is>
-          <t>3 / 8 MT ✗</t>
+          <t>4 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R153" s="4" t="inlineStr">
@@ -13873,22 +13873,22 @@
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>32 NB</t>
+          <t>40 NB</t>
         </is>
       </c>
       <c r="G154" s="4" t="n">
         <v>2.5</v>
       </c>
       <c r="H154" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I154" s="4" t="inlineStr">
         <is>
-          <t>2.5 × 128 mm</t>
+          <t>2.3 × 150 mm</t>
         </is>
       </c>
       <c r="J154" s="5" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="K154" s="5" t="n">
         <v>49</v>
@@ -13903,16 +13903,16 @@
         <v>0</v>
       </c>
       <c r="O154" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>11 / 20 MT ✗</t>
+          <t>14 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q154" s="4" t="inlineStr">
         <is>
-          <t>4 / 8 MT ✗</t>
+          <t>5 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R154" s="4" t="inlineStr">
@@ -13961,25 +13961,25 @@
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>40 NB</t>
+          <t>50 NB</t>
         </is>
       </c>
       <c r="G155" s="4" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="H155" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I155" s="4" t="inlineStr">
         <is>
-          <t>2.3 × 150 mm</t>
+          <t>2 × 186 mm</t>
         </is>
       </c>
       <c r="J155" s="5" t="n">
-        <v>4.74</v>
+        <v>0</v>
       </c>
       <c r="K155" s="5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L155" s="5" t="n">
         <v>0</v>
@@ -13991,16 +13991,16 @@
         <v>0</v>
       </c>
       <c r="O155" s="5" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>14 / 20 MT ✗</t>
+          <t>9 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q155" s="4" t="inlineStr">
         <is>
-          <t>5 / 8 MT ✗</t>
+          <t>2 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R155" s="4" t="inlineStr">
@@ -14053,14 +14053,14 @@
         </is>
       </c>
       <c r="G156" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H156" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I156" s="4" t="inlineStr">
         <is>
-          <t>2 × 186 mm</t>
+          <t>4 × 182 mm</t>
         </is>
       </c>
       <c r="J156" s="5" t="n">
@@ -14137,25 +14137,25 @@
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>50 NB</t>
+          <t>65 NB</t>
         </is>
       </c>
       <c r="G157" s="4" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="H157" s="5" t="n">
         <v>2</v>
       </c>
       <c r="I157" s="4" t="inlineStr">
         <is>
-          <t>4 × 182 mm</t>
+          <t>2.5 × 235 mm</t>
         </is>
       </c>
       <c r="J157" s="5" t="n">
-        <v>0</v>
+        <v>9.33</v>
       </c>
       <c r="K157" s="5" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="L157" s="5" t="n">
         <v>0</v>
@@ -14171,7 +14171,7 @@
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>9 / 20 MT ✗</t>
+          <t>2 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q157" s="4" t="inlineStr">
@@ -14225,25 +14225,25 @@
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>65 NB</t>
+          <t>80 NB</t>
         </is>
       </c>
       <c r="G158" s="4" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="H158" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I158" s="4" t="inlineStr">
         <is>
-          <t>2.5 × 235 mm</t>
+          <t>4 × 270 mm</t>
         </is>
       </c>
       <c r="J158" s="5" t="n">
-        <v>9.33</v>
+        <v>0</v>
       </c>
       <c r="K158" s="5" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="L158" s="5" t="n">
         <v>0</v>
@@ -14255,16 +14255,16 @@
         <v>0</v>
       </c>
       <c r="O158" s="5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>2 / 20 MT ✗</t>
+          <t>7 / 20 MT ✗</t>
         </is>
       </c>
       <c r="Q158" s="4" t="inlineStr">
         <is>
-          <t>2 / 8 MT ✗</t>
+          <t>7 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R158" s="4" t="inlineStr">
@@ -14308,23 +14308,23 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>CHS</t>
+          <t>SHS</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>80 NB</t>
+          <t>20x20</t>
         </is>
       </c>
       <c r="G159" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H159" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I159" s="4" t="inlineStr">
         <is>
-          <t>4 × 270 mm</t>
+          <t>2 × 76 mm</t>
         </is>
       </c>
       <c r="J159" s="5" t="n">
@@ -14343,26 +14343,26 @@
         <v>0</v>
       </c>
       <c r="O159" s="5" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>7 / 20 MT ✗</t>
+          <t>27 / 20 MT ✓</t>
         </is>
       </c>
       <c r="Q159" s="4" t="inlineStr">
         <is>
-          <t>7 / 8 MT ✗</t>
+          <t>9 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R159" s="4" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S159" s="4" t="inlineStr">
         <is>
-          <t>DEFER — family short of min campaign</t>
+          <t>DEFER — under gauge floor</t>
         </is>
       </c>
       <c r="T159" s="4" t="inlineStr">
@@ -14687,7 +14687,7 @@
         <v>9.33</v>
       </c>
       <c r="K163" s="5" t="n">
-        <v>11.5</v>
+        <v>49</v>
       </c>
       <c r="L163" s="5" t="n">
         <v>0</v>
@@ -14888,12 +14888,12 @@
       </c>
       <c r="Q165" s="4" t="inlineStr">
         <is>
-          <t>15 / 12 MT ✓</t>
+          <t>15 / 8 MT ✓</t>
         </is>
       </c>
       <c r="R165" s="4" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S165" s="4" t="inlineStr">
@@ -15064,12 +15064,12 @@
       </c>
       <c r="Q167" s="4" t="inlineStr">
         <is>
-          <t>5 / 12 MT ✗</t>
+          <t>5 / 8 MT ✗</t>
         </is>
       </c>
       <c r="R167" s="4" t="inlineStr">
         <is>
-          <t>BAND EDGE</t>
+          <t>in band</t>
         </is>
       </c>
       <c r="S167" s="4" t="inlineStr">
@@ -15131,7 +15131,7 @@
         <v>0</v>
       </c>
       <c r="K168" s="5" t="n">
-        <v>11.5</v>
+        <v>49</v>
       </c>
       <c r="L168" s="5" t="n">
         <v>0</v>
@@ -15219,7 +15219,7 @@
         <v>0</v>
       </c>
       <c r="K169" s="5" t="n">
-        <v>18.23</v>
+        <v>75.97</v>
       </c>
       <c r="L169" s="5" t="n">
         <v>0</v>
@@ -15240,12 +15240,12 @@
       </c>
       <c r="Q169" s="4" t="inlineStr">
         <is>
-          <t>3 / 8 MT ✗</t>
+          <t>3 / 12 MT ✗</t>
         </is>
       </c>
       <c r="R169" s="4" t="inlineStr">
         <is>
-          <t>in band</t>
+          <t>BAND EDGE</t>
         </is>
       </c>
       <c r="S169" s="4" t="inlineStr">
@@ -15487,7 +15487,7 @@
         <v>31.34</v>
       </c>
       <c r="K172" s="5" t="n">
-        <v>0.04</v>
+        <v>49</v>
       </c>
       <c r="L172" s="5" t="n">
         <v>0</v>
@@ -15751,7 +15751,7 @@
         <v>0</v>
       </c>
       <c r="K175" s="5" t="n">
-        <v>0.04</v>
+        <v>49</v>
       </c>
       <c r="L175" s="5" t="n">
         <v>0</v>
@@ -15839,7 +15839,7 @@
         <v>0</v>
       </c>
       <c r="K176" s="5" t="n">
-        <v>18.23</v>
+        <v>75.97</v>
       </c>
       <c r="L176" s="5" t="n">
         <v>0</v>
@@ -16039,7 +16039,7 @@
         </is>
       </c>
       <c r="H184" s="14" t="n">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="185">
@@ -16049,7 +16049,7 @@
         </is>
       </c>
       <c r="H185" s="14" t="n">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="186">

--- a/reports/Rolling-Plan-NoStock-2026-10-26.xlsx
+++ b/reports/Rolling-Plan-NoStock-2026-10-26.xlsx
@@ -519,7 +519,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>As on 26 Oct 2026. Demand = "QTY LEFT WITH NO STOCK" (Indent − Dispatch, 1–25 Oct) from QtyLeft_Stock_vs_NoStock_Oct26.xlsx. Coil = unconsumed baby coils (242, 904.52 MT) + unslit mother coils (900.69 MT), live Supabase. Rules: PT Operating System Pack — ADR-0001, campaign-planning-parameters R1–R8.</t>
+          <t>Coil position as at 27 Oct 2026 05:19 UTC. Demand = "QTY LEFT WITH NO STOCK" (Indent - Dispatch, 1-25 Oct) from QtyLeft_Stock_vs_NoStock_Oct26.xlsx. Coil = 239 unconsumed baby coils (890.23 MT) + unslit mother coils (877.17 MT), live Supabase. Anything slit or produced after that snapshot is NOT reflected - re-run before issuing. Rules: PT Operating System Pack - ADR-0001, campaign-planning-parameters R1-R8.</t>
         </is>
       </c>
     </row>
@@ -533,7 +533,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Thresholds PROPOSED, not signed off: min campaign 20 MT/family, gauge floor 8 MT/cell (×1.5 = 12 MT outside the 3–8% T/D band), coil→tube yield 96%. Verified against the live database on 26 Oct 2026.</t>
+          <t>Thresholds PROPOSED, not signed off: min campaign 20 MT/family, gauge floor 8 MT/cell (×1.5 = 12 MT outside the 3–8% T/D band), coil→tube yield 96%. Independently verified against the live database at the snapshot above.</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C8" s="6" t="inlineStr">
@@ -975,7 +975,7 @@
         <v>13.16</v>
       </c>
       <c r="K10" s="7" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L10" s="7" t="n">
         <v>8.33</v>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -1067,7 +1067,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="9" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L11" s="9" t="n">
         <v>0</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C13" s="8" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C14" s="6" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>Hyderabad 12.5</t>
+          <t>Lepakshi 7.9 + Hyderabad 4.6</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1347,7 +1347,7 @@
         <v>27.72</v>
       </c>
       <c r="K14" s="7" t="n">
-        <v>196.51</v>
+        <v>173</v>
       </c>
       <c r="L14" s="7" t="n">
         <v>0</v>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>27 Oct</t>
         </is>
       </c>
       <c r="C16" s="6" t="inlineStr">
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="J16" s="7" t="n">
-        <v>4.12</v>
+        <v>12.82</v>
       </c>
       <c r="K16" s="7" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L16" s="7" t="n">
-        <v>4.12</v>
+        <v>8.33</v>
       </c>
       <c r="M16" s="7" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="N16" s="7" t="n">
         <v>8</v>
@@ -1573,7 +1573,7 @@
       <c r="U16" s="6" t="inlineStr"/>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>South width from its own 2.8mm run (3mm never run here)</t>
+          <t>South has slit this 3 of 3 times</t>
         </is>
       </c>
     </row>
@@ -1585,7 +1585,7 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>29 Oct</t>
+          <t>30 Oct</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -5672,10 +5672,10 @@
         </is>
       </c>
       <c r="J61" s="11" t="n">
-        <v>13.63</v>
+        <v>15.41</v>
       </c>
       <c r="K61" s="11" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L61" s="11" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>0</v>
       </c>
       <c r="K62" s="11" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L62" s="11" t="n">
         <v>0</v>
@@ -5851,7 +5851,7 @@
         <v>7.76</v>
       </c>
       <c r="K63" s="11" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L63" s="11" t="n">
         <v>0</v>
@@ -5936,10 +5936,10 @@
         </is>
       </c>
       <c r="J64" s="11" t="n">
-        <v>4.12</v>
+        <v>12.82</v>
       </c>
       <c r="K64" s="11" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L64" s="11" t="n">
         <v>0</v>
@@ -6291,7 +6291,7 @@
         <v>0</v>
       </c>
       <c r="K68" s="11" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L68" s="11" t="n">
         <v>0</v>
@@ -6555,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="K71" s="11" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L71" s="11" t="n">
         <v>0</v>
@@ -6731,7 +6731,7 @@
         <v>0</v>
       </c>
       <c r="K73" s="11" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L73" s="11" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
         <v>0</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>196.51</v>
+        <v>173</v>
       </c>
       <c r="L77" s="11" t="n">
         <v>0</v>
@@ -12567,7 +12567,7 @@
         <v>13.16</v>
       </c>
       <c r="K139" s="5" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L139" s="5" t="n">
         <v>0</v>
@@ -12835,7 +12835,7 @@
         <v>0</v>
       </c>
       <c r="K142" s="5" t="n">
-        <v>196.51</v>
+        <v>173</v>
       </c>
       <c r="L142" s="5" t="n">
         <v>0</v>
@@ -12923,7 +12923,7 @@
         <v>0</v>
       </c>
       <c r="K143" s="5" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L143" s="5" t="n">
         <v>0</v>
@@ -13011,7 +13011,7 @@
         <v>0</v>
       </c>
       <c r="K144" s="5" t="n">
-        <v>149.12</v>
+        <v>125.61</v>
       </c>
       <c r="L144" s="5" t="n">
         <v>0</v>
@@ -14152,7 +14152,7 @@
         </is>
       </c>
       <c r="J157" s="5" t="n">
-        <v>9.33</v>
+        <v>0</v>
       </c>
       <c r="K157" s="5" t="n">
         <v>49</v>
@@ -14684,7 +14684,7 @@
         </is>
       </c>
       <c r="J163" s="5" t="n">
-        <v>9.33</v>
+        <v>0</v>
       </c>
       <c r="K163" s="5" t="n">
         <v>49</v>
@@ -15983,10 +15983,10 @@
         <v>2138</v>
       </c>
       <c r="L178" s="13" t="n">
-        <v>204.4</v>
+        <v>208.6</v>
       </c>
       <c r="M178" s="13" t="n">
-        <v>326</v>
+        <v>321.8</v>
       </c>
       <c r="N178" s="13" t="n">
         <v>509.2</v>
@@ -16089,7 +16089,7 @@
         </is>
       </c>
       <c r="H189" s="14" t="n">
-        <v>1805.21</v>
+        <v>1767.41</v>
       </c>
     </row>
     <row r="190">
@@ -16109,7 +16109,7 @@
         </is>
       </c>
       <c r="H191" s="14" t="n">
-        <v>1274.78</v>
+        <v>1236.98</v>
       </c>
     </row>
     <row r="193">

--- a/reports/Rolling-Plan-NoStock-2026-10-26.xlsx
+++ b/reports/Rolling-Plan-NoStock-2026-10-26.xlsx
@@ -526,7 +526,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Sequence: rounds then shapes, diameter ascending (R6); gauge thin→thick inside a family (R5); coil in the yard before coil to be slit (R7.1); ONE window per family (ADR-0001), at most 12 (South) / 5 (West) families per week — the most either region has actually run in one week. Mother coil is on site: slit + buffer = ready 29 Oct, so it can serve W1 — the "Runs from" column dates those lots. The 14-day lead applies only to coil that must be bought.</t>
+          <t>Sequence: rounds then shapes, diameter ascending (R6); gauge thin→thick inside a family (R5); coil in the yard before coil to be slit (R7.1); ONE window per family (ADR-0001), at most 12 (South) / 5 (West) families per week — the most either region has actually run in one week. Mother coil is on site: slit + buffer = ready 30 Oct, so it can serve W1 — the "Runs from" column dates those lots. The 14-day lead applies only to coil that must be bought.</t>
         </is>
       </c>
     </row>
@@ -16122,7 +16122,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>12 cells have no slitting spec at all (no width ever established for that size, anywhere): SOUTH CHS 100 NB; SOUTH RHS 95x25; WEST RHS 172x92; WEST RHS 240x120; WEST SHS 180x180; WEST SHS 32x32. Establish the slit width and these become plannable.</t>
+          <t>32 cells have no slit width established anywhere. 12 of them are blocked on the width alone (SOUTH CHS 100 NB; SOUTH RHS 95x25; WEST RHS 172x92; WEST RHS 240x120; WEST SHS 180x180; WEST SHS 32x32) and become plannable once it is set; the other 20 are blocked on a missing SKU master row first, so they need both.</t>
         </is>
       </c>
     </row>
